--- a/public/exports-from-60/29189382.xlsx
+++ b/public/exports-from-60/29189382.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5666,30 +5666,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevold 10</t>
+          <t xml:space="preserve">Enghavevej 11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J76">
-        <v>480</v>
+        <v>779</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054733</t>
+          <t xml:space="preserve">200055336</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-10</t>
+          <t xml:space="preserve">2021-12-01</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Hedevej 251</t>
+          <t xml:space="preserve">Hovedgaden 116P</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526510</t>
+          <t xml:space="preserve">1800942</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J77">
-        <v>258</v>
+        <v>144</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054944</t>
+          <t xml:space="preserve">200055687</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-17</t>
+          <t xml:space="preserve">2021-12-09</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 11</t>
+          <t xml:space="preserve">Hovedgaden 116S</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">1800942</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J78">
-        <v>779</v>
+        <v>136</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055336</t>
+          <t xml:space="preserve">200055687</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-01</t>
+          <t xml:space="preserve">2021-12-09</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 116P</t>
+          <t xml:space="preserve">Hovedgaden 116U</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J79">
@@ -5966,30 +5966,30 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 116S</t>
+          <t xml:space="preserve">Bøgstedvej 255</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800942</t>
+          <t xml:space="preserve">9118872</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055687</t>
+          <t xml:space="preserve">200055917</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-09</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,30 +6041,30 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 116U</t>
+          <t xml:space="preserve">Fuglsigvej 23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800942</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J81">
-        <v>144</v>
+        <v>1992</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055687</t>
+          <t xml:space="preserve">200055924</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-09</t>
+          <t xml:space="preserve">2021-12-15</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,30 +6116,30 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgstedvej 255</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118872</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J82">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055917</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 23</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>1992</v>
+        <v>852</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055924</t>
+          <t xml:space="preserve">200055932</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6281,11 +6281,11 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J84">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6356,11 +6356,11 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J85">
-        <v>852</v>
+        <v>470</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6431,11 +6431,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J86">
-        <v>223</v>
+        <v>1347</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J87">
-        <v>470</v>
+        <v>422</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J88">
-        <v>1347</v>
+        <v>98</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J89">
-        <v>422</v>
+        <v>575</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>98</v>
+        <v>394</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vestergade 33</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">3214642</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055932</t>
+          <t xml:space="preserve">200055931</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6881,11 +6881,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J92">
-        <v>394</v>
+        <v>1647</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Ulvmosevej 3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">3150176</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>585</v>
+        <v>499</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">200055998</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,30 +7016,30 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 33</t>
+          <t xml:space="preserve">Vendelbogade 10A</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214642</t>
+          <t xml:space="preserve">3169983</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>1647</v>
+        <v>5060</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055931</t>
+          <t xml:space="preserve">200056002</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-15</t>
+          <t xml:space="preserve">2021-12-16</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvmosevej 3</t>
+          <t xml:space="preserve">Jerupvej 485A</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150176</t>
+          <t xml:space="preserve">403345, 403346</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>499</v>
+        <v>1366</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055998</t>
+          <t xml:space="preserve">200056210</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 10A</t>
+          <t xml:space="preserve">Markedsgade 3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7181,15 +7181,15 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>5060</v>
+        <v>164</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056002</t>
+          <t xml:space="preserve">200056198</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-16</t>
+          <t xml:space="preserve">2021-12-21</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,40 +7241,40 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerupvej 485A</t>
+          <t xml:space="preserve">Poulstrup Skolevej 5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">403345, 403346</t>
+          <t xml:space="preserve">753473, 3217725</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
-        <v>1366</v>
+        <v>1765</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056210</t>
+          <t xml:space="preserve">311126737</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-21</t>
+          <t xml:space="preserve">2025-07-29</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,40 +7316,40 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedsgade 3</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169983</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J98">
-        <v>164</v>
+        <v>656</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056198</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-21</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,17 +7391,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrenstedvej 54</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980081</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="J99">
-        <v>560</v>
+        <v>3761</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311044984</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-26</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,30 +7466,30 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poulstrup Skolevej 5</t>
+          <t xml:space="preserve">Halvejen 4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">753473, 3217725</t>
+          <t xml:space="preserve">752877, 3178980</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J100">
-        <v>1765</v>
+        <v>801</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311126737</t>
+          <t xml:space="preserve">311132372</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-29</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,30 +7551,30 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">3178967</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>656</v>
+        <v>1631</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311175796</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2026-05-11</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,40 +7616,40 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Slettingenvej 51</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">1403342</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J102">
-        <v>3761</v>
+        <v>85</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311199559</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,40 +7691,40 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 4</t>
+          <t xml:space="preserve">Slettingenvej 51</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">752877, 3178980</t>
+          <t xml:space="preserve">1403342</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J103">
-        <v>801</v>
+        <v>98</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132372</t>
+          <t xml:space="preserve">311199555</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgen Fibigersgade 22</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178967</t>
+          <t xml:space="preserve">5521204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,31 +7785,31 @@
         </is>
       </c>
       <c r="J104">
-        <v>1631</v>
+        <v>4153</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311175796</t>
+          <t xml:space="preserve">311213844</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-11</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettingenvej 51</t>
+          <t xml:space="preserve">Amtmandstoften 2A</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,40 +7851,40 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403342</t>
+          <t xml:space="preserve">5521383</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>85</v>
+        <v>1332</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199559</t>
+          <t xml:space="preserve">311224295</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2027-01-24</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettingenvej 51</t>
+          <t xml:space="preserve">Asdalvej 14</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,40 +7926,40 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403342</t>
+          <t xml:space="preserve">3159619</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>98</v>
+        <v>3719</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199555</t>
+          <t xml:space="preserve">311466015</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521204</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="J107">
-        <v>4153</v>
+        <v>2764</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213844</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amtmandstoften 2A</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,30 +8076,30 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521383</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>1332</v>
+        <v>1021</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224295</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-24</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asdalvej 14</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159619</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J109">
-        <v>3719</v>
+        <v>4161</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466015</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J110">
-        <v>2764</v>
+        <v>808</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J111">
-        <v>1021</v>
+        <v>153</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466005</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>4161</v>
+        <v>1395</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,20 +8451,20 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J113">
-        <v>808</v>
+        <v>598</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466011</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J114">
-        <v>153</v>
+        <v>2086</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466005</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J115">
-        <v>1395</v>
+        <v>1240</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8681,15 +8681,15 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J116">
-        <v>598</v>
+        <v>1325</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466011</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8756,11 +8756,11 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J117">
-        <v>2086</v>
+        <v>2005</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8831,11 +8831,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J118">
-        <v>1240</v>
+        <v>1055</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,20 +8901,20 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>1325</v>
+        <v>3691</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J120">
-        <v>2005</v>
+        <v>1680</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J121">
-        <v>1055</v>
+        <v>1073</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9131,11 +9131,11 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J122">
-        <v>3691</v>
+        <v>1780</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Børge Christensens V 4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,30 +9201,30 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">1507102</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>1680</v>
+        <v>6875</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477652</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Idrætsmarken 15A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,30 +9276,30 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>1073</v>
+        <v>717</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Idrætsmarken 15B</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,30 +9351,30 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>1780</v>
+        <v>162</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Børge Christensens V 4</t>
+          <t xml:space="preserve">Vellingshøjvej 380B</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,20 +9426,20 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507102</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J126">
-        <v>6875</v>
+        <v>2644</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477652</t>
+          <t xml:space="preserve">311477664</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,40 +9491,40 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15A</t>
+          <t xml:space="preserve">Finlandsgade 12</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J127">
-        <v>717</v>
+        <v>464</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311485016</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15B</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="J128">
-        <v>162</v>
+        <v>1477</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311485012</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,40 +9641,40 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 380B</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
-        <v>2644</v>
+        <v>1933</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477664</t>
+          <t xml:space="preserve">311485012</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,30 +9716,30 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsgade 12</t>
+          <t xml:space="preserve">Norgesvej 6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">5524762</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>464</v>
+        <v>8112</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485016</t>
+          <t xml:space="preserve">311485007</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Rævskærvej 8</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9806,11 +9806,11 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J131">
-        <v>1477</v>
+        <v>684</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>1933</v>
+        <v>842</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,30 +9941,30 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 6</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524762</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J133">
-        <v>8112</v>
+        <v>919</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485007</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævskærvej 8</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>684</v>
+        <v>495</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10106,11 +10106,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J135">
-        <v>842</v>
+        <v>1088</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>919</v>
+        <v>85</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J137">
-        <v>495</v>
+        <v>966</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,20 +10326,20 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J138">
-        <v>1088</v>
+        <v>1942</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J139">
-        <v>85</v>
+        <v>634</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J140">
-        <v>966</v>
+        <v>1974</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J141">
-        <v>1942</v>
+        <v>668</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vendelbogade 7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3170022</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>634</v>
+        <v>3071</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485008</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vestbakken 12</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3210318</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J143">
-        <v>1974</v>
+        <v>785</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485005</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>668</v>
+        <v>528</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 7</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,20 +10851,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170022</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J145">
-        <v>3071</v>
+        <v>941</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485008</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,30 +10916,30 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestbakken 12</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3210318</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J146">
-        <v>785</v>
+        <v>2112</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485005</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J147">
-        <v>528</v>
+        <v>458</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J148">
-        <v>941</v>
+        <v>602</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J149">
-        <v>2112</v>
+        <v>393</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J150">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J151">
-        <v>602</v>
+        <v>812</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J152">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>440</v>
+        <v>1230</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11531,11 +11531,11 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J154">
-        <v>812</v>
+        <v>946</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11606,11 +11606,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J155">
-        <v>406</v>
+        <v>1206</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Islandsgade 23</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11681,11 +11681,11 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J156">
-        <v>1230</v>
+        <v>240</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11741,30 +11741,30 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Stendyssevej 80F</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J157">
-        <v>946</v>
+        <v>534</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485121</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,30 +11816,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Aage Holms Vej 6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">7881176</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>1206</v>
+        <v>760</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494575</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 23</t>
+          <t xml:space="preserve">Enghavevej 2A</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,20 +11901,20 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>240</v>
+        <v>349</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,30 +11966,30 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80F</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
-        <v>534</v>
+        <v>886</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485121</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 6</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">7881176</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J161">
-        <v>760</v>
+        <v>430</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494575</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2A</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J162">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12206,11 +12206,11 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J163">
-        <v>886</v>
+        <v>507</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12266,30 +12266,30 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Fuglsigvej 21</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">5527904</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>430</v>
+        <v>586</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494579</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,30 +12341,30 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Græshedevej 26</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">3204366</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>219</v>
+        <v>536</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494558</t>
+          <t xml:space="preserve">311494576</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,30 +12416,30 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Grønningen 1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J166">
-        <v>507</v>
+        <v>1399</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494556</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 21</t>
+          <t xml:space="preserve">H C Andersens Vej 1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527904</t>
+          <t xml:space="preserve">3168485</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>586</v>
+        <v>669</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494579</t>
+          <t xml:space="preserve">311494573</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshedevej 26</t>
+          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204366</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J168">
-        <v>536</v>
+        <v>455</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494576</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,30 +12641,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 1</t>
+          <t xml:space="preserve">Kingosvej 10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>1399</v>
+        <v>1336</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494556</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Andersens Vej 1</t>
+          <t xml:space="preserve">Lonesvej 192</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168485</t>
+          <t xml:space="preserve">8719671</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>669</v>
+        <v>707</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494573</t>
+          <t xml:space="preserve">311494577</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
+          <t xml:space="preserve">Lundtoftevej 48</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">5527621</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>455</v>
+        <v>381</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494568</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,17 +12866,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kingosvej 10</t>
+          <t xml:space="preserve">Nørrebro 27</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,11 +12885,11 @@
         </is>
       </c>
       <c r="J172">
-        <v>1336</v>
+        <v>2334</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lonesvej 192</t>
+          <t xml:space="preserve">Sct Knuds Alle 10</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719671</t>
+          <t xml:space="preserve">9797238</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,11 +12960,11 @@
         </is>
       </c>
       <c r="J173">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494577</t>
+          <t xml:space="preserve">311494566</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 48</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527621</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,11 +13035,11 @@
         </is>
       </c>
       <c r="J174">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494568</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 27</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J175">
-        <v>2334</v>
+        <v>87</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Knuds Alle 10</t>
+          <t xml:space="preserve">Skagensvej 137</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9797238</t>
+          <t xml:space="preserve">1800309</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>766</v>
+        <v>549</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494566</t>
+          <t xml:space="preserve">311494569</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J177">
-        <v>393</v>
+        <v>3417</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,11 +13335,11 @@
         </is>
       </c>
       <c r="J178">
-        <v>87</v>
+        <v>269</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494580</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 137</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800309</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J179">
-        <v>549</v>
+        <v>415</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494569</t>
+          <t xml:space="preserve">311494581</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J180">
-        <v>3417</v>
+        <v>88</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494582</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,30 +13541,30 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>269</v>
+        <v>8698</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494580</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J182">
-        <v>415</v>
+        <v>1003</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494581</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,40 +13691,40 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Idræts Alle 1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">100218261</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J183">
-        <v>88</v>
+        <v>8190</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494582</t>
+          <t xml:space="preserve">311566030</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8</t>
+          <t xml:space="preserve">Vanggårdsgade 17</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">3178968</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,21 +13785,21 @@
         </is>
       </c>
       <c r="J184">
-        <v>8698</v>
+        <v>751</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311625072</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Bygge-syn ApS</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2032-09-02</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,40 +13841,40 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
+          <t xml:space="preserve">Palleskær Engvej 5</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">5526859</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J185">
-        <v>1003</v>
+        <v>2155</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311650741</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,17 +13916,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 1</t>
+          <t xml:space="preserve">Nordbovej 5</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">100218261</t>
+          <t xml:space="preserve">5522955</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>8190</v>
+        <v>2615</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566030</t>
+          <t xml:space="preserve">311669639</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,17 +13991,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 17</t>
+          <t xml:space="preserve">Hvidegårds Ager 25</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178968</t>
+          <t xml:space="preserve">1507298</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,21 +14010,21 @@
         </is>
       </c>
       <c r="J187">
-        <v>751</v>
+        <v>395</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625072</t>
+          <t xml:space="preserve">311674591</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge-syn ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-02</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palleskær Engvej 5</t>
+          <t xml:space="preserve">P Nørkjærs Plads 16</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,30 +14076,30 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526859</t>
+          <t xml:space="preserve">403893</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J188">
-        <v>2155</v>
+        <v>149</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650741</t>
+          <t xml:space="preserve">311743993</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordbovej 5</t>
+          <t xml:space="preserve">Brændingen 2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522955</t>
+          <t xml:space="preserve">3218381</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>2615</v>
+        <v>299</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669639</t>
+          <t xml:space="preserve">311790590</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,17 +14216,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidegårds Ager 25</t>
+          <t xml:space="preserve">Ved Banen 8</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507298</t>
+          <t xml:space="preserve">100606984</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,21 +14235,21 @@
         </is>
       </c>
       <c r="J190">
-        <v>395</v>
+        <v>10174</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674591</t>
+          <t xml:space="preserve">311794226</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2034-10-29</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,40 +14291,40 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">P Nørkjærs Plads 16</t>
+          <t xml:space="preserve">Højskolevej 11</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">403893</t>
+          <t xml:space="preserve">9796718</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743993</t>
+          <t xml:space="preserve">311879279</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech Solutions A/S</t>
+          <t xml:space="preserve">Bygge-syn ApS</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 2</t>
+          <t xml:space="preserve">Brændingen 12A</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218381</t>
+          <t xml:space="preserve">402929, 402930</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,21 +14385,21 @@
         </is>
       </c>
       <c r="J192">
-        <v>299</v>
+        <v>874</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790590</t>
+          <t xml:space="preserve">311885675</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Banen 8</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">100606984</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,21 +14460,21 @@
         </is>
       </c>
       <c r="J193">
-        <v>10174</v>
+        <v>2230</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311794226</t>
+          <t xml:space="preserve">311885676</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-29</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,40 +14516,40 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højskolevej 11</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9796718</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J194">
-        <v>103</v>
+        <v>1492</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879279</t>
+          <t xml:space="preserve">311885677</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge-syn ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 12A</t>
+          <t xml:space="preserve">Bugten 4</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">402929, 402930</t>
+          <t xml:space="preserve">3162830</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>874</v>
+        <v>432</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885675</t>
+          <t xml:space="preserve">311885642</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Dronningensgade 31</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">5521240</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>2230</v>
+        <v>473</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885676</t>
+          <t xml:space="preserve">311885656</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Fynsgade 13</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">5521521</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>1492</v>
+        <v>3681</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885677</t>
+          <t xml:space="preserve">311885649</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugten 4</t>
+          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162830</t>
+          <t xml:space="preserve">3217023</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>432</v>
+        <v>269</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885642</t>
+          <t xml:space="preserve">311885687</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 31</t>
+          <t xml:space="preserve">Jernbanegade 8C</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521240</t>
+          <t xml:space="preserve">3213957</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,11 +14910,11 @@
         </is>
       </c>
       <c r="J199">
-        <v>473</v>
+        <v>194</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885656</t>
+          <t xml:space="preserve">311885689</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 13</t>
+          <t xml:space="preserve">Overgade 7</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521521</t>
+          <t xml:space="preserve">5521462</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>3681</v>
+        <v>667</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885649</t>
+          <t xml:space="preserve">311885657</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,17 +15041,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
+          <t xml:space="preserve">Skagerakvej 3</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3217023</t>
+          <t xml:space="preserve">3178136</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,11 +15060,11 @@
         </is>
       </c>
       <c r="J201">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885687</t>
+          <t xml:space="preserve">311885633</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,17 +15116,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 8C</t>
+          <t xml:space="preserve">Svanelundsbakken 25</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3213957</t>
+          <t xml:space="preserve">5527785</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,11 +15135,11 @@
         </is>
       </c>
       <c r="J202">
-        <v>194</v>
+        <v>4178</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885689</t>
+          <t xml:space="preserve">311885653</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 7</t>
+          <t xml:space="preserve">Søndergade 20A</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521462</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J203">
-        <v>667</v>
+        <v>515</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885657</t>
+          <t xml:space="preserve">311885634</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15266,17 +15266,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 3</t>
+          <t xml:space="preserve">Fuglsigvej 52</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178136</t>
+          <t xml:space="preserve">1808737</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15285,11 +15285,11 @@
         </is>
       </c>
       <c r="J204">
-        <v>278</v>
+        <v>402</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885633</t>
+          <t xml:space="preserve">311886408</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanelundsbakken 25</t>
+          <t xml:space="preserve">Hirtshalsvej 17</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527785</t>
+          <t xml:space="preserve">7201111</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15360,11 +15360,11 @@
         </is>
       </c>
       <c r="J205">
-        <v>4178</v>
+        <v>494</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885653</t>
+          <t xml:space="preserve">311886401</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20A</t>
+          <t xml:space="preserve">Tværvej 9A</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>515</v>
+        <v>256</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885634</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,30 +15491,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 52</t>
+          <t xml:space="preserve">Tværvej 9E</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808737</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J207">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886408</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 17</t>
+          <t xml:space="preserve">Femhøje 5A</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7201111</t>
+          <t xml:space="preserve">428228, 428229, 428230</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>494</v>
+        <v>3279</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886401</t>
+          <t xml:space="preserve">311886888</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,17 +15641,17 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9A</t>
+          <t xml:space="preserve">N C Jensensgade 2A</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">3177962</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886891</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,17 +15716,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9E</t>
+          <t xml:space="preserve">N C Jensensgade 2B</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">3177962</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,11 +15735,11 @@
         </is>
       </c>
       <c r="J210">
-        <v>382</v>
+        <v>88</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886891</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,17 +15791,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femhøje 5A</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">428228, 428229, 428230</t>
+          <t xml:space="preserve">3214506</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>3279</v>
+        <v>4371</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886888</t>
+          <t xml:space="preserve">311886892</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,17 +15866,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">N C Jensensgade 2A</t>
+          <t xml:space="preserve">Valmuevej 3A</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177962</t>
+          <t xml:space="preserve">3214536</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15885,11 +15885,11 @@
         </is>
       </c>
       <c r="J212">
-        <v>222</v>
+        <v>820</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886891</t>
+          <t xml:space="preserve">311886893</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,30 +15941,30 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">N C Jensensgade 2B</t>
+          <t xml:space="preserve">Tannisbugtvej 24D</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177962</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J213">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886891</t>
+          <t xml:space="preserve">311887386</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-13</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,30 +16016,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Tannisbugtvej 24F</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214506</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J214">
-        <v>4371</v>
+        <v>130</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886892</t>
+          <t xml:space="preserve">311887386</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-13</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valmuevej 3A</t>
+          <t xml:space="preserve">Østergade 30A</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214536</t>
+          <t xml:space="preserve">407002</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>820</v>
+        <v>1091</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886893</t>
+          <t xml:space="preserve">311887712</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,30 +16166,30 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24D</t>
+          <t xml:space="preserve">Østergade 30B</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J216">
-        <v>130</v>
+        <v>518</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887386</t>
+          <t xml:space="preserve">311887713</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-13</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,30 +16241,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24F</t>
+          <t xml:space="preserve">Østergade 30C</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J217">
-        <v>130</v>
+        <v>1132</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887386</t>
+          <t xml:space="preserve">311887715</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-13</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30A</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,11 +16335,11 @@
         </is>
       </c>
       <c r="J218">
-        <v>1091</v>
+        <v>265</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887712</t>
+          <t xml:space="preserve">311888133</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30B</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>518</v>
+        <v>393</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887713</t>
+          <t xml:space="preserve">311888130</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,30 +16466,30 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30C</t>
+          <t xml:space="preserve">Tannisbugtvej 24A</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J220">
-        <v>1132</v>
+        <v>1086</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887715</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,30 +16541,30 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24B</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J221">
-        <v>265</v>
+        <v>994</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888133</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,30 +16616,30 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24C</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J222">
-        <v>393</v>
+        <v>611</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888130</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,17 +16691,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24A</t>
+          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">409430, 409431</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>1086</v>
+        <v>7175</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888761</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16766,30 +16766,30 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24B</t>
+          <t xml:space="preserve">Tykskovvej 4</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">9547586</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J224">
-        <v>994</v>
+        <v>4610</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888732</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16841,30 +16841,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24C</t>
+          <t xml:space="preserve">Vikingbanke 12</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">8971909</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J225">
-        <v>611</v>
+        <v>2534</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888727</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16916,30 +16916,30 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
+          <t xml:space="preserve">Færøvej 12</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">409430, 409431</t>
+          <t xml:space="preserve">3170285</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J226">
-        <v>7175</v>
+        <v>201</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888761</t>
+          <t xml:space="preserve">311890124</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tykskovvej 4</t>
+          <t xml:space="preserve">Færøvej 4</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547586</t>
+          <t xml:space="preserve">3170285</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17010,11 +17010,11 @@
         </is>
       </c>
       <c r="J227">
-        <v>4610</v>
+        <v>134</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888732</t>
+          <t xml:space="preserve">311890124</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,30 +17066,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingbanke 12</t>
+          <t xml:space="preserve">Færøvej 8</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971909</t>
+          <t xml:space="preserve">3170285</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J228">
-        <v>2534</v>
+        <v>134</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888727</t>
+          <t xml:space="preserve">311890124</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,30 +17141,30 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 12</t>
+          <t xml:space="preserve">Albert Ginges Vej 15</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170285</t>
+          <t xml:space="preserve">5525116</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J229">
-        <v>201</v>
+        <v>360</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890124</t>
+          <t xml:space="preserve">311892238</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,17 +17216,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 4</t>
+          <t xml:space="preserve">Annasvej 14</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170285</t>
+          <t xml:space="preserve">5528700</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17235,11 +17235,11 @@
         </is>
       </c>
       <c r="J230">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890124</t>
+          <t xml:space="preserve">311892239</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,30 +17291,30 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 8</t>
+          <t xml:space="preserve">Bøgstedvej 245</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170285</t>
+          <t xml:space="preserve">7007775</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J231">
-        <v>134</v>
+        <v>481</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890124</t>
+          <t xml:space="preserve">311892240</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Ginges Vej 15</t>
+          <t xml:space="preserve">Skagen Landevej 113</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525116</t>
+          <t xml:space="preserve">3159903</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,11 +17385,11 @@
         </is>
       </c>
       <c r="J232">
-        <v>360</v>
+        <v>752</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892238</t>
+          <t xml:space="preserve">311892241</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Annasvej 14</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5528700</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17460,11 +17460,11 @@
         </is>
       </c>
       <c r="J233">
-        <v>99</v>
+        <v>310</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892239</t>
+          <t xml:space="preserve">311892242</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgstedvej 245</t>
+          <t xml:space="preserve">Østergade 9A</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007775</t>
+          <t xml:space="preserve">5521643</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,11 +17535,11 @@
         </is>
       </c>
       <c r="J234">
-        <v>481</v>
+        <v>1986</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892240</t>
+          <t xml:space="preserve">311892821</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,17 +17591,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagen Landevej 113</t>
+          <t xml:space="preserve">Brændingen 4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159903</t>
+          <t xml:space="preserve">3218373</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,11 +17610,11 @@
         </is>
       </c>
       <c r="J235">
-        <v>752</v>
+        <v>455</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892241</t>
+          <t xml:space="preserve">311893154</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,30 +17666,30 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Sejlstrupvej 10</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>310</v>
+        <v>184</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892242</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,17 +17741,17 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 9A</t>
+          <t xml:space="preserve">Sejlstrupvej 8</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521643</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -17760,11 +17760,11 @@
         </is>
       </c>
       <c r="J237">
-        <v>1986</v>
+        <v>337</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892821</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,17 +17816,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 4</t>
+          <t xml:space="preserve">Toftagervej 1</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218373</t>
+          <t xml:space="preserve">3177487</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,11 +17835,11 @@
         </is>
       </c>
       <c r="J238">
-        <v>455</v>
+        <v>1813</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893154</t>
+          <t xml:space="preserve">311893155</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,30 +17891,30 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 10</t>
+          <t xml:space="preserve">Korshøjvænget 9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">10018016</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>184</v>
+        <v>735</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311893922</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-14</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 8</t>
+          <t xml:space="preserve">Studievej 10</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,11 +17985,11 @@
         </is>
       </c>
       <c r="J240">
-        <v>337</v>
+        <v>4559</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311894478</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,30 +18041,30 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftagervej 1</t>
+          <t xml:space="preserve">Studievej 7</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177487</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J241">
-        <v>1813</v>
+        <v>129</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893155</t>
+          <t xml:space="preserve">311894479</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,30 +18116,30 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korshøjvænget 9</t>
+          <t xml:space="preserve">Studievej 8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">10018016</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J242">
-        <v>735</v>
+        <v>369</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893922</t>
+          <t xml:space="preserve">311894481</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-14</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 10</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J243">
-        <v>4559</v>
+        <v>2284</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894478</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,30 +18266,30 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 7</t>
+          <t xml:space="preserve">Skagensvej 200B</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J244">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894479</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,30 +18341,30 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 8</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>369</v>
+        <v>5053</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894481</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18431,11 +18431,11 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J246">
-        <v>2284</v>
+        <v>996</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200B</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,20 +18501,20 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J247">
-        <v>109</v>
+        <v>857</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895836</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,20 +18576,20 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J248">
-        <v>5053</v>
+        <v>1934</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,20 +18651,20 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J249">
-        <v>996</v>
+        <v>1420</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18731,15 +18731,15 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J250">
-        <v>857</v>
+        <v>584</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895836</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,30 +18791,30 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Stationsvej 12</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">3218579</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>1934</v>
+        <v>1289</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311898010</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-30</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Bistrupvej 3</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18876,20 +18876,20 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">5525288</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J252">
-        <v>1420</v>
+        <v>4361</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311898618</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Idræts Alle 45</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18951,20 +18951,20 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">9885530</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>584</v>
+        <v>372</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311901519</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,17 +19016,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 12</t>
+          <t xml:space="preserve">Sdr Vråvej 5</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218579</t>
+          <t xml:space="preserve">3214265</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -19035,11 +19035,11 @@
         </is>
       </c>
       <c r="J254">
-        <v>1289</v>
+        <v>2793</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898010</t>
+          <t xml:space="preserve">311901495</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-30</t>
+          <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvej 3</t>
+          <t xml:space="preserve">Idræts Alle 45B</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,20 +19101,20 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525288</t>
+          <t xml:space="preserve">5522709</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J255">
-        <v>4361</v>
+        <v>105</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898618</t>
+          <t xml:space="preserve">311912369</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45</t>
+          <t xml:space="preserve">Skolevangen 46</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,20 +19176,20 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885530</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J256">
-        <v>372</v>
+        <v>1334</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901519</t>
+          <t xml:space="preserve">311918196</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-15</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,17 +19241,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr Vråvej 5</t>
+          <t xml:space="preserve">Taagholtvej 170</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214265</t>
+          <t xml:space="preserve">1403213</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -19260,11 +19260,11 @@
         </is>
       </c>
       <c r="J257">
-        <v>2793</v>
+        <v>407</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901495</t>
+          <t xml:space="preserve">311918197</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-15</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45B</t>
+          <t xml:space="preserve">Torvegade 15</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522709</t>
+          <t xml:space="preserve">1800354</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J258">
-        <v>105</v>
+        <v>940</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912369</t>
+          <t xml:space="preserve">311918198</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,30 +19391,30 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 46</t>
+          <t xml:space="preserve">Vanggårdsgade 10B</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">7075274</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J259">
-        <v>1334</v>
+        <v>117</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918196</t>
+          <t xml:space="preserve">311918201</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19466,17 +19466,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taagholtvej 170</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403213</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -19485,11 +19485,11 @@
         </is>
       </c>
       <c r="J260">
-        <v>407</v>
+        <v>251</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918197</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19541,30 +19541,30 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 15</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800354</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J261">
-        <v>940</v>
+        <v>567</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918198</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19616,17 +19616,17 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 10B</t>
+          <t xml:space="preserve">Vellingshøjvej 391A</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">7075274</t>
+          <t xml:space="preserve">3167523</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -19635,11 +19635,11 @@
         </is>
       </c>
       <c r="J262">
-        <v>117</v>
+        <v>427</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918201</t>
+          <t xml:space="preserve">311918170</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Idræts Alle 45B</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">5522709</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -19710,11 +19710,11 @@
         </is>
       </c>
       <c r="J263">
-        <v>251</v>
+        <v>112</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311921769</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,30 +19766,30 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Skagerakvej 2</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">3178269</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J264">
-        <v>567</v>
+        <v>518</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311921781</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391A</t>
+          <t xml:space="preserve">Elsagervej 27A</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">3167523</t>
+          <t xml:space="preserve">7871638</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,11 +19860,11 @@
         </is>
       </c>
       <c r="J265">
-        <v>427</v>
+        <v>1723</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918170</t>
+          <t xml:space="preserve">311922371</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45B</t>
+          <t xml:space="preserve">Elsagervej 44</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522709</t>
+          <t xml:space="preserve">5522933</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,11 +19935,11 @@
         </is>
       </c>
       <c r="J266">
-        <v>112</v>
+        <v>1040</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921769</t>
+          <t xml:space="preserve">311922368</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,30 +19991,30 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 2</t>
+          <t xml:space="preserve">Frederikshavnsvej 70B</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178269</t>
+          <t xml:space="preserve">5526485</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J267">
-        <v>518</v>
+        <v>149</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921781</t>
+          <t xml:space="preserve">311922281</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 27A</t>
+          <t xml:space="preserve">Georg Jensens Vej 12</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">7871638</t>
+          <t xml:space="preserve">5524990</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -20085,11 +20085,11 @@
         </is>
       </c>
       <c r="J268">
-        <v>1723</v>
+        <v>2910</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922371</t>
+          <t xml:space="preserve">311922280</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 44</t>
+          <t xml:space="preserve">Grønningen 8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522933</t>
+          <t xml:space="preserve">7002365</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,11 +20160,11 @@
         </is>
       </c>
       <c r="J269">
-        <v>1040</v>
+        <v>367</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922368</t>
+          <t xml:space="preserve">311922282</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederikshavnsvej 70B</t>
+          <t xml:space="preserve">Tjørnevej 6</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20226,20 +20226,20 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526485</t>
+          <t xml:space="preserve">7010644</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J270">
-        <v>149</v>
+        <v>380</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922281</t>
+          <t xml:space="preserve">311922366</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georg Jensens Vej 12</t>
+          <t xml:space="preserve">Aage Holms Vej 8</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524990</t>
+          <t xml:space="preserve">9938684</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -20310,11 +20310,11 @@
         </is>
       </c>
       <c r="J271">
-        <v>2910</v>
+        <v>4353</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922280</t>
+          <t xml:space="preserve">311922647</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,17 +20366,17 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 8</t>
+          <t xml:space="preserve">Hovedgaden 116A</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002365</t>
+          <t xml:space="preserve">1800942</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -20385,11 +20385,11 @@
         </is>
       </c>
       <c r="J272">
-        <v>367</v>
+        <v>763</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922282</t>
+          <t xml:space="preserve">311922848</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 6</t>
+          <t xml:space="preserve">Vester Thirupvej 55A</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010644</t>
+          <t xml:space="preserve">10014113</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -20460,11 +20460,11 @@
         </is>
       </c>
       <c r="J273">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922366</t>
+          <t xml:space="preserve">311922665</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,30 +20516,30 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 8</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9938684</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J274">
-        <v>4353</v>
+        <v>375</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922647</t>
+          <t xml:space="preserve">311923108</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,17 +20591,17 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 116A</t>
+          <t xml:space="preserve">Grønnevold 10</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800942</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -20610,11 +20610,11 @@
         </is>
       </c>
       <c r="J275">
-        <v>763</v>
+        <v>480</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922848</t>
+          <t xml:space="preserve">311925965</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Thirupvej 55A</t>
+          <t xml:space="preserve">Vester Hedevej 251</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">10014113</t>
+          <t xml:space="preserve">5526510</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20685,11 +20685,11 @@
         </is>
       </c>
       <c r="J276">
-        <v>448</v>
+        <v>258</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922665</t>
+          <t xml:space="preserve">311925892</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,30 +20741,30 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vrenstedvej 54</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">9980081</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J277">
-        <v>375</v>
+        <v>560</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923108</t>
+          <t xml:space="preserve">311925986</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">

--- a/public/exports-from-60/29189382.xlsx
+++ b/public/exports-from-60/29189382.xlsx
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettingenvej 51</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,20 +7326,20 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403342</t>
+          <t xml:space="preserve">5521204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>85</v>
+        <v>4153</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199559</t>
+          <t xml:space="preserve">311213844</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slettingenvej 51</t>
+          <t xml:space="preserve">Amtmandstoften 2A</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,40 +7401,40 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403342</t>
+          <t xml:space="preserve">5521383</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>98</v>
+        <v>1332</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199555</t>
+          <t xml:space="preserve">311224295</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2027-01-24</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">Asdalvej 14</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521204</t>
+          <t xml:space="preserve">3159619</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="J100">
-        <v>4153</v>
+        <v>3719</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311213844</t>
+          <t xml:space="preserve">311466015</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPH Energi A/S</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-23</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amtmandstoften 2A</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521383</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="J101">
-        <v>1332</v>
+        <v>2764</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224295</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-24</t>
+          <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asdalvej 14</t>
+          <t xml:space="preserve">Fuglsigvej 1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,20 +7626,20 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159619</t>
+          <t xml:space="preserve">5527832</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J102">
-        <v>3719</v>
+        <v>1021</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466015</t>
+          <t xml:space="preserve">311474034</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J103">
-        <v>2764</v>
+        <v>4161</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7781,11 +7781,11 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J104">
-        <v>1021</v>
+        <v>808</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,20 +7851,20 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J105">
-        <v>4161</v>
+        <v>153</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466005</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 1</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527832</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J106">
-        <v>808</v>
+        <v>1395</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474034</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Skolevangen 44</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J107">
-        <v>153</v>
+        <v>598</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466005</t>
+          <t xml:space="preserve">311466011</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>1395</v>
+        <v>2086</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8156,15 +8156,15 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J109">
-        <v>598</v>
+        <v>1240</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466011</t>
+          <t xml:space="preserve">311466010</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J110">
-        <v>2086</v>
+        <v>1325</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8306,11 +8306,11 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J111">
-        <v>1240</v>
+        <v>2005</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8381,11 +8381,11 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J112">
-        <v>1325</v>
+        <v>1055</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,20 +8451,20 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>2005</v>
+        <v>3691</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 44</t>
+          <t xml:space="preserve">Nordens Alle 15</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">8719612</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J114">
-        <v>1055</v>
+        <v>1680</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466010</t>
+          <t xml:space="preserve">311466350</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-08</t>
+          <t xml:space="preserve">2030-10-09</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J115">
-        <v>3691</v>
+        <v>1073</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8681,11 +8681,11 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J116">
-        <v>1680</v>
+        <v>1780</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Børge Christensens V 4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,30 +8751,30 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">1507102</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J117">
-        <v>1073</v>
+        <v>6875</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477652</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordens Alle 15</t>
+          <t xml:space="preserve">Idrætsmarken 15A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,30 +8826,30 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719612</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J118">
-        <v>1780</v>
+        <v>717</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466350</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-09</t>
+          <t xml:space="preserve">2030-11-05</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Børge Christensens V 4</t>
+          <t xml:space="preserve">Idrætsmarken 15B</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507102</t>
+          <t xml:space="preserve">3204339</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>6875</v>
+        <v>162</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477652</t>
+          <t xml:space="preserve">311477661</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15A</t>
+          <t xml:space="preserve">Vellingshøjvej 380B</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J120">
-        <v>717</v>
+        <v>2644</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311477664</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-11-23</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,40 +9041,40 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsmarken 15B</t>
+          <t xml:space="preserve">Finlandsgade 12</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204339</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J121">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477661</t>
+          <t xml:space="preserve">311485016</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-05</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,40 +9116,40 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 380B</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>2644</v>
+        <v>1477</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477664</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-23</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandsgade 12</t>
+          <t xml:space="preserve">Hovedvejen 35</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3172356</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>464</v>
+        <v>1933</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485016</t>
+          <t xml:space="preserve">311485009</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Norgesvej 6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">5524762</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>1477</v>
+        <v>8112</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485007</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 35</t>
+          <t xml:space="preserve">Rævskærvej 8</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J125">
-        <v>1933</v>
+        <v>684</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 6</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524762</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>8112</v>
+        <v>842</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485007</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævskærvej 8</t>
+          <t xml:space="preserve">Stendyssevej 80A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3172356</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J127">
-        <v>684</v>
+        <v>919</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485009</t>
+          <t xml:space="preserve">311485010</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9581,11 +9581,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J128">
-        <v>842</v>
+        <v>495</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9656,11 +9656,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J129">
-        <v>919</v>
+        <v>1088</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>495</v>
+        <v>85</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80A</t>
+          <t xml:space="preserve">Ved Skolen 2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3177633</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J131">
-        <v>1088</v>
+        <v>966</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485010</t>
+          <t xml:space="preserve">311485013</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9881,11 +9881,11 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J132">
-        <v>85</v>
+        <v>1942</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9956,11 +9956,11 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J133">
-        <v>966</v>
+        <v>634</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10031,11 +10031,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J134">
-        <v>1942</v>
+        <v>1974</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10106,11 +10106,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J135">
-        <v>634</v>
+        <v>668</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vendelbogade 7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3170022</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>1974</v>
+        <v>3071</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485008</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,30 +10241,30 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Skolen 2</t>
+          <t xml:space="preserve">Vestbakken 12</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177633</t>
+          <t xml:space="preserve">3210318</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J137">
-        <v>668</v>
+        <v>785</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485013</t>
+          <t xml:space="preserve">311485005</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendelbogade 7</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170022</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,11 +10335,11 @@
         </is>
       </c>
       <c r="J138">
-        <v>3071</v>
+        <v>528</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485008</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestbakken 12</t>
+          <t xml:space="preserve">Islandsgade 21</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3210318</t>
+          <t xml:space="preserve">3169519</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J139">
-        <v>785</v>
+        <v>941</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485005</t>
+          <t xml:space="preserve">311485160</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-28</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J140">
-        <v>528</v>
+        <v>2112</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10556,11 +10556,11 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J141">
-        <v>941</v>
+        <v>458</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J142">
-        <v>2112</v>
+        <v>602</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10706,11 +10706,11 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J143">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J144">
-        <v>602</v>
+        <v>440</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10856,11 +10856,11 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J145">
-        <v>393</v>
+        <v>812</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J146">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J147">
-        <v>812</v>
+        <v>1230</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J148">
-        <v>406</v>
+        <v>946</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>1230</v>
+        <v>1206</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Islandsgade 23</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J150">
-        <v>946</v>
+        <v>240</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 21</t>
+          <t xml:space="preserve">Stendyssevej 80F</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">3158047</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J151">
-        <v>1206</v>
+        <v>534</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311485121</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,30 +11366,30 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsgade 23</t>
+          <t xml:space="preserve">Aage Holms Vej 6</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3169519</t>
+          <t xml:space="preserve">7881176</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>240</v>
+        <v>760</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485160</t>
+          <t xml:space="preserve">311494575</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,30 +11441,30 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendyssevej 80F</t>
+          <t xml:space="preserve">Enghavevej 2A</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3158047</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>534</v>
+        <v>349</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311485121</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-28</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,30 +11516,30 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 6</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7881176</t>
+          <t xml:space="preserve">3150088</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J154">
-        <v>760</v>
+        <v>886</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494575</t>
+          <t xml:space="preserve">311494562</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2A</t>
+          <t xml:space="preserve">Enghavevej 2B</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J155">
-        <v>349</v>
+        <v>430</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11681,15 +11681,15 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J156">
-        <v>886</v>
+        <v>219</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494558</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2B</t>
+          <t xml:space="preserve">Enghavevej 2C</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11756,11 +11756,11 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J157">
-        <v>430</v>
+        <v>507</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11816,30 +11816,30 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Fuglsigvej 21</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">5527904</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>219</v>
+        <v>586</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494558</t>
+          <t xml:space="preserve">311494579</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 2C</t>
+          <t xml:space="preserve">Græshedevej 26</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3150088</t>
+          <t xml:space="preserve">3204366</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494562</t>
+          <t xml:space="preserve">311494576</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,30 +11966,30 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 21</t>
+          <t xml:space="preserve">Grønningen 1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527904</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J160">
-        <v>586</v>
+        <v>1399</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494579</t>
+          <t xml:space="preserve">311494556</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græshedevej 26</t>
+          <t xml:space="preserve">H C Andersens Vej 1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204366</t>
+          <t xml:space="preserve">3168485</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>536</v>
+        <v>669</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494576</t>
+          <t xml:space="preserve">311494573</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,30 +12116,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 1</t>
+          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J162">
-        <v>1399</v>
+        <v>455</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494556</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">H C Andersens Vej 1</t>
+          <t xml:space="preserve">Kingosvej 10</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3168485</t>
+          <t xml:space="preserve">5524305</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>669</v>
+        <v>1336</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494573</t>
+          <t xml:space="preserve">311494571</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Ewalds Vej 4</t>
+          <t xml:space="preserve">Lonesvej 192</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">8719671</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>455</v>
+        <v>707</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494577</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kingosvej 10</t>
+          <t xml:space="preserve">Lundtoftevej 48</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524305</t>
+          <t xml:space="preserve">5527621</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>1336</v>
+        <v>381</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494571</t>
+          <t xml:space="preserve">311494568</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,17 +12416,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lonesvej 192</t>
+          <t xml:space="preserve">Nørrebro 27</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719671</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>707</v>
+        <v>2334</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494577</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 48</t>
+          <t xml:space="preserve">Sct Knuds Alle 10</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527621</t>
+          <t xml:space="preserve">9797238</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>381</v>
+        <v>766</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494568</t>
+          <t xml:space="preserve">311494566</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,17 +12566,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 27</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12585,11 +12585,11 @@
         </is>
       </c>
       <c r="J168">
-        <v>2334</v>
+        <v>393</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct Knuds Alle 10</t>
+          <t xml:space="preserve">Skagensvej 131</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">9797238</t>
+          <t xml:space="preserve">5524072</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>766</v>
+        <v>87</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494566</t>
+          <t xml:space="preserve">311494570</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">Skagensvej 137</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">1800309</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>393</v>
+        <v>549</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494569</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,30 +12791,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 131</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524072</t>
+          <t xml:space="preserve">3143046</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J171">
-        <v>87</v>
+        <v>3417</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494570</t>
+          <t xml:space="preserve">311494563</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 137</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800309</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>549</v>
+        <v>269</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494569</t>
+          <t xml:space="preserve">311494580</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,30 +12941,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3143046</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J173">
-        <v>3417</v>
+        <v>415</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494563</t>
+          <t xml:space="preserve">311494581</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13031,15 +13031,15 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J174">
-        <v>269</v>
+        <v>88</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494580</t>
+          <t xml:space="preserve">311494582</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>415</v>
+        <v>8698</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494581</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">8719497</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J176">
-        <v>88</v>
+        <v>1003</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494582</t>
+          <t xml:space="preserve">311495777</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-02-16</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8</t>
+          <t xml:space="preserve">Idræts Alle 1</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">100218261</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -13260,21 +13260,21 @@
         </is>
       </c>
       <c r="J177">
-        <v>8698</v>
+        <v>8190</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311566030</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,40 +13316,40 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrejlev Klostervej 8A</t>
+          <t xml:space="preserve">Vanggårdsgade 17</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719497</t>
+          <t xml:space="preserve">3178968</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>1003</v>
+        <v>751</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311495777</t>
+          <t xml:space="preserve">311625072</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Bygge-syn ApS</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-16</t>
+          <t xml:space="preserve">2032-09-02</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,17 +13391,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 1</t>
+          <t xml:space="preserve">Palleskær Engvej 5</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">100218261</t>
+          <t xml:space="preserve">5526859</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -13410,11 +13410,11 @@
         </is>
       </c>
       <c r="J179">
-        <v>8190</v>
+        <v>2155</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566030</t>
+          <t xml:space="preserve">311650741</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 17</t>
+          <t xml:space="preserve">Nordbovej 5</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178968</t>
+          <t xml:space="preserve">5522955</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,21 +13485,21 @@
         </is>
       </c>
       <c r="J180">
-        <v>751</v>
+        <v>2615</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311625072</t>
+          <t xml:space="preserve">311669639</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge-syn ApS</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-02</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palleskær Engvej 5</t>
+          <t xml:space="preserve">Hvidegårds Ager 25</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526859</t>
+          <t xml:space="preserve">1507298</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,21 +13560,21 @@
         </is>
       </c>
       <c r="J181">
-        <v>2155</v>
+        <v>395</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650741</t>
+          <t xml:space="preserve">311674591</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordbovej 5</t>
+          <t xml:space="preserve">P Nørkjærs Plads 16</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,30 +13626,30 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522955</t>
+          <t xml:space="preserve">403893</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J182">
-        <v>2615</v>
+        <v>149</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669639</t>
+          <t xml:space="preserve">311743993</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,17 +13691,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidegårds Ager 25</t>
+          <t xml:space="preserve">Brændingen 2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1507298</t>
+          <t xml:space="preserve">3218381</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,21 +13710,21 @@
         </is>
       </c>
       <c r="J183">
-        <v>395</v>
+        <v>299</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674591</t>
+          <t xml:space="preserve">311790590</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,40 +13766,40 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">P Nørkjærs Plads 16</t>
+          <t xml:space="preserve">Ved Banen 8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">403893</t>
+          <t xml:space="preserve">100606984</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J184">
-        <v>149</v>
+        <v>10174</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743993</t>
+          <t xml:space="preserve">311794226</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech Solutions A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-10-29</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 2</t>
+          <t xml:space="preserve">Højskolevej 11</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218381</t>
+          <t xml:space="preserve">9796718</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,21 +13860,21 @@
         </is>
       </c>
       <c r="J185">
-        <v>299</v>
+        <v>103</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790590</t>
+          <t xml:space="preserve">311879279</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Bygge-syn ApS</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,17 +13916,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Banen 8</t>
+          <t xml:space="preserve">Brændingen 12A</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">100606984</t>
+          <t xml:space="preserve">402929, 402930</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,21 +13935,21 @@
         </is>
       </c>
       <c r="J186">
-        <v>10174</v>
+        <v>874</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311794226</t>
+          <t xml:space="preserve">311885675</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-29</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,17 +13991,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højskolevej 11</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9796718</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,21 +14010,21 @@
         </is>
       </c>
       <c r="J187">
-        <v>103</v>
+        <v>2230</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879279</t>
+          <t xml:space="preserve">311885676</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge-syn ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 12A</t>
+          <t xml:space="preserve">Brændingen 8</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,20 +14076,20 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">402929, 402930</t>
+          <t xml:space="preserve">3218374</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>874</v>
+        <v>1492</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885675</t>
+          <t xml:space="preserve">311885677</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Bugten 4</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">3162830</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>2230</v>
+        <v>432</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885676</t>
+          <t xml:space="preserve">311885642</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,30 +14216,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 8</t>
+          <t xml:space="preserve">Dronningensgade 31</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218374</t>
+          <t xml:space="preserve">5521240</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>1492</v>
+        <v>473</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885677</t>
+          <t xml:space="preserve">311885656</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugten 4</t>
+          <t xml:space="preserve">Fynsgade 13</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162830</t>
+          <t xml:space="preserve">5521521</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>432</v>
+        <v>3681</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885642</t>
+          <t xml:space="preserve">311885649</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14366,17 +14366,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 31</t>
+          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521240</t>
+          <t xml:space="preserve">3217023</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>473</v>
+        <v>269</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885656</t>
+          <t xml:space="preserve">311885687</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 13</t>
+          <t xml:space="preserve">Jernbanegade 8C</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521521</t>
+          <t xml:space="preserve">3213957</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>3681</v>
+        <v>194</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885649</t>
+          <t xml:space="preserve">311885689</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14516,17 +14516,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Rønnebjergvej 9</t>
+          <t xml:space="preserve">Overgade 7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3217023</t>
+          <t xml:space="preserve">5521462</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>269</v>
+        <v>667</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885687</t>
+          <t xml:space="preserve">311885657</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 8C</t>
+          <t xml:space="preserve">Skagerakvej 3</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3213957</t>
+          <t xml:space="preserve">3178136</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885689</t>
+          <t xml:space="preserve">311885633</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 7</t>
+          <t xml:space="preserve">Svanelundsbakken 25</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521462</t>
+          <t xml:space="preserve">5527785</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>667</v>
+        <v>4178</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885657</t>
+          <t xml:space="preserve">311885653</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 3</t>
+          <t xml:space="preserve">Søndergade 20A</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,20 +14751,20 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178136</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J197">
-        <v>278</v>
+        <v>515</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885633</t>
+          <t xml:space="preserve">311885634</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanelundsbakken 25</t>
+          <t xml:space="preserve">Fuglsigvej 52</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527785</t>
+          <t xml:space="preserve">1808737</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>4178</v>
+        <v>402</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885653</t>
+          <t xml:space="preserve">311886408</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,30 +14891,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20A</t>
+          <t xml:space="preserve">Hirtshalsvej 17</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">7201111</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>515</v>
+        <v>494</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885634</t>
+          <t xml:space="preserve">311886401</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsigvej 52</t>
+          <t xml:space="preserve">Tværvej 9A</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808737</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>402</v>
+        <v>256</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886408</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,30 +15041,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 17</t>
+          <t xml:space="preserve">Tværvej 9E</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7201111</t>
+          <t xml:space="preserve">3209805</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J201">
-        <v>494</v>
+        <v>382</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886401</t>
+          <t xml:space="preserve">311886406</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,17 +15116,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9A</t>
+          <t xml:space="preserve">Femhøje 5A</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">428228, 428229, 428230</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,11 +15135,11 @@
         </is>
       </c>
       <c r="J202">
-        <v>256</v>
+        <v>3279</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886888</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 9E</t>
+          <t xml:space="preserve">N C Jensensgade 2A</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3209805</t>
+          <t xml:space="preserve">3177962</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>382</v>
+        <v>222</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886406</t>
+          <t xml:space="preserve">311886891</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femhøje 5A</t>
+          <t xml:space="preserve">N C Jensensgade 2B</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">428228, 428229, 428230</t>
+          <t xml:space="preserve">3177962</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J204">
-        <v>3279</v>
+        <v>88</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886888</t>
+          <t xml:space="preserve">311886891</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,17 +15341,17 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">N C Jensensgade 2A</t>
+          <t xml:space="preserve">Stadionvej 6</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177962</t>
+          <t xml:space="preserve">3214506</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15360,11 +15360,11 @@
         </is>
       </c>
       <c r="J205">
-        <v>222</v>
+        <v>4371</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886891</t>
+          <t xml:space="preserve">311886892</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">N C Jensensgade 2B</t>
+          <t xml:space="preserve">Valmuevej 3A</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177962</t>
+          <t xml:space="preserve">3214536</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>88</v>
+        <v>820</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886891</t>
+          <t xml:space="preserve">311886893</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,30 +15491,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6</t>
+          <t xml:space="preserve">Tannisbugtvej 24D</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214506</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J207">
-        <v>4371</v>
+        <v>130</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886892</t>
+          <t xml:space="preserve">311887386</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-13</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,30 +15566,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valmuevej 3A</t>
+          <t xml:space="preserve">Tannisbugtvej 24F</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214536</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J208">
-        <v>820</v>
+        <v>130</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886893</t>
+          <t xml:space="preserve">311887386</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-13</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,30 +15641,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24D</t>
+          <t xml:space="preserve">Østergade 30A</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">407002</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>130</v>
+        <v>1091</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887386</t>
+          <t xml:space="preserve">311887712</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-13</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,30 +15716,30 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24F</t>
+          <t xml:space="preserve">Østergade 30B</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J210">
-        <v>130</v>
+        <v>518</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887386</t>
+          <t xml:space="preserve">311887713</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-13</t>
+          <t xml:space="preserve">2036-03-16</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30A</t>
+          <t xml:space="preserve">Østergade 30C</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,20 +15801,20 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002</t>
+          <t xml:space="preserve">407002, 407003</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J211">
-        <v>1091</v>
+        <v>1132</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887712</t>
+          <t xml:space="preserve">311887715</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30B</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>518</v>
+        <v>265</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887713</t>
+          <t xml:space="preserve">311888133</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 30C</t>
+          <t xml:space="preserve">Søndergade 20</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">407002, 407003</t>
+          <t xml:space="preserve">3178283</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J213">
-        <v>1132</v>
+        <v>393</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311887715</t>
+          <t xml:space="preserve">311888130</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-16</t>
+          <t xml:space="preserve">2036-03-17</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24A</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>265</v>
+        <v>1086</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888133</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 20</t>
+          <t xml:space="preserve">Tannisbugtvej 24B</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9881</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178283</t>
+          <t xml:space="preserve">3155505</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>393</v>
+        <v>994</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888130</t>
+          <t xml:space="preserve">311888742</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-17</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24A</t>
+          <t xml:space="preserve">Tannisbugtvej 24C</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J216">
-        <v>1086</v>
+        <v>611</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16241,30 +16241,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24B</t>
+          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">409430, 409431</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J217">
-        <v>994</v>
+        <v>7175</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888761</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16316,30 +16316,30 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tannisbugtvej 24C</t>
+          <t xml:space="preserve">Tykskovvej 4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">9881</t>
+          <t xml:space="preserve">9830</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3155505</t>
+          <t xml:space="preserve">9547586</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J218">
-        <v>611</v>
+        <v>4610</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888742</t>
+          <t xml:space="preserve">311888732</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16391,17 +16391,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Morilds Vej 11A</t>
+          <t xml:space="preserve">Vikingbanke 12</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">409430, 409431</t>
+          <t xml:space="preserve">8971909</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>7175</v>
+        <v>2534</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888761</t>
+          <t xml:space="preserve">311888727</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16466,30 +16466,30 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tykskovvej 4</t>
+          <t xml:space="preserve">Færøvej 12</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547586</t>
+          <t xml:space="preserve">3170285</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J220">
-        <v>4610</v>
+        <v>201</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888732</t>
+          <t xml:space="preserve">311890124</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,17 +16541,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingbanke 12</t>
+          <t xml:space="preserve">Færøvej 4</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971909</t>
+          <t xml:space="preserve">3170285</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>2534</v>
+        <v>134</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888727</t>
+          <t xml:space="preserve">311890124</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 12</t>
+          <t xml:space="preserve">Færøvej 8</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J222">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16691,17 +16691,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 4</t>
+          <t xml:space="preserve">Albert Ginges Vej 15</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170285</t>
+          <t xml:space="preserve">5525116</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>134</v>
+        <v>360</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890124</t>
+          <t xml:space="preserve">311892238</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,30 +16766,30 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 8</t>
+          <t xml:space="preserve">Annasvej 14</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3170285</t>
+          <t xml:space="preserve">5528700</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J224">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890124</t>
+          <t xml:space="preserve">311892239</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Ginges Vej 15</t>
+          <t xml:space="preserve">Bøgstedvej 245</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525116</t>
+          <t xml:space="preserve">7007775</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16860,11 +16860,11 @@
         </is>
       </c>
       <c r="J225">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892238</t>
+          <t xml:space="preserve">311892240</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Annasvej 14</t>
+          <t xml:space="preserve">Skagen Landevej 113</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5528700</t>
+          <t xml:space="preserve">3159903</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,11 +16935,11 @@
         </is>
       </c>
       <c r="J226">
-        <v>99</v>
+        <v>752</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892239</t>
+          <t xml:space="preserve">311892241</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgstedvej 245</t>
+          <t xml:space="preserve">Spangkærvej 79</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7007775</t>
+          <t xml:space="preserve">1403144</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17010,11 +17010,11 @@
         </is>
       </c>
       <c r="J227">
-        <v>481</v>
+        <v>310</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892240</t>
+          <t xml:space="preserve">311892242</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagen Landevej 113</t>
+          <t xml:space="preserve">Østergade 9A</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">3159903</t>
+          <t xml:space="preserve">5521643</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -17085,11 +17085,11 @@
         </is>
       </c>
       <c r="J228">
-        <v>752</v>
+        <v>1986</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892241</t>
+          <t xml:space="preserve">311892821</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,17 +17141,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spangkærvej 79</t>
+          <t xml:space="preserve">Brændingen 4</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403144</t>
+          <t xml:space="preserve">3218373</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,11 +17160,11 @@
         </is>
       </c>
       <c r="J229">
-        <v>310</v>
+        <v>455</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892242</t>
+          <t xml:space="preserve">311893154</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,30 +17216,30 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 9A</t>
+          <t xml:space="preserve">Sejlstrupvej 10</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521643</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J230">
-        <v>1986</v>
+        <v>184</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892821</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-09</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændingen 4</t>
+          <t xml:space="preserve">Sejlstrupvej 8</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218373</t>
+          <t xml:space="preserve">3161657</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,11 +17310,11 @@
         </is>
       </c>
       <c r="J231">
-        <v>455</v>
+        <v>337</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893154</t>
+          <t xml:space="preserve">311893152</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,30 +17366,30 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 10</t>
+          <t xml:space="preserve">Toftagervej 1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">3177487</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J232">
-        <v>184</v>
+        <v>1813</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311893155</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17441,17 +17441,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejlstrupvej 8</t>
+          <t xml:space="preserve">Korshøjvænget 9</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">3161657</t>
+          <t xml:space="preserve">10018016</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17460,11 +17460,11 @@
         </is>
       </c>
       <c r="J233">
-        <v>337</v>
+        <v>735</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893152</t>
+          <t xml:space="preserve">311893922</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-14</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,17 +17516,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftagervej 1</t>
+          <t xml:space="preserve">Studievej 10</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">3177487</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,11 +17535,11 @@
         </is>
       </c>
       <c r="J234">
-        <v>1813</v>
+        <v>4559</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893155</t>
+          <t xml:space="preserve">311894478</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-09</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,30 +17591,30 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korshøjvænget 9</t>
+          <t xml:space="preserve">Studievej 7</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">10018016</t>
+          <t xml:space="preserve">8540210</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J235">
-        <v>735</v>
+        <v>129</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893922</t>
+          <t xml:space="preserve">311894479</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-14</t>
+          <t xml:space="preserve">2036-04-16</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 10</t>
+          <t xml:space="preserve">Studievej 8</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17681,15 +17681,15 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>4559</v>
+        <v>369</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894478</t>
+          <t xml:space="preserve">311894481</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 7</t>
+          <t xml:space="preserve">Skagensvej 200A</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J237">
-        <v>129</v>
+        <v>2284</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894479</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,17 +17816,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studievej 8</t>
+          <t xml:space="preserve">Skagensvej 200B</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540210</t>
+          <t xml:space="preserve">9028182</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,11 +17835,11 @@
         </is>
       </c>
       <c r="J238">
-        <v>369</v>
+        <v>109</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894481</t>
+          <t xml:space="preserve">311895956</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-16</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200A</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17906,11 +17906,11 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>2284</v>
+        <v>5053</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagensvej 200B</t>
+          <t xml:space="preserve">Vellingshøjvej 368</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17981,11 +17981,11 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J240">
-        <v>109</v>
+        <v>996</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -18060,11 +18060,11 @@
         </is>
       </c>
       <c r="J241">
-        <v>5053</v>
+        <v>857</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895836</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 368</t>
+          <t xml:space="preserve">Ålborgvej 49</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,20 +18126,20 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">9028182</t>
+          <t xml:space="preserve">5527862</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J242">
-        <v>996</v>
+        <v>1934</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895956</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18206,15 +18206,15 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J243">
-        <v>857</v>
+        <v>1420</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895836</t>
+          <t xml:space="preserve">311895837</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18281,11 +18281,11 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J244">
-        <v>1934</v>
+        <v>584</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -18341,30 +18341,30 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Stationsvej 12</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">3218579</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>1420</v>
+        <v>1289</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311898010</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-30</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålborgvej 49</t>
+          <t xml:space="preserve">Bistrupvej 3</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,20 +18426,20 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5527862</t>
+          <t xml:space="preserve">5525288</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J246">
-        <v>584</v>
+        <v>4361</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895837</t>
+          <t xml:space="preserve">311898618</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,17 +18491,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 12</t>
+          <t xml:space="preserve">Idræts Alle 45</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218579</t>
+          <t xml:space="preserve">9885530</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,11 +18510,11 @@
         </is>
       </c>
       <c r="J247">
-        <v>1289</v>
+        <v>372</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898010</t>
+          <t xml:space="preserve">311901519</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-30</t>
+          <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,17 +18566,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvej 3</t>
+          <t xml:space="preserve">Sdr Vråvej 5</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525288</t>
+          <t xml:space="preserve">3214265</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,11 +18585,11 @@
         </is>
       </c>
       <c r="J248">
-        <v>4361</v>
+        <v>2793</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898618</t>
+          <t xml:space="preserve">311901495</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-05-15</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45</t>
+          <t xml:space="preserve">Idræts Alle 45B</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,20 +18651,20 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">9885530</t>
+          <t xml:space="preserve">5522709</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J249">
-        <v>372</v>
+        <v>105</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901519</t>
+          <t xml:space="preserve">311912369</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-15</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,30 +18716,30 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr Vråvej 5</t>
+          <t xml:space="preserve">Skolevangen 46</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214265</t>
+          <t xml:space="preserve">5525100</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J250">
-        <v>2793</v>
+        <v>1334</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311901495</t>
+          <t xml:space="preserve">311918196</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-15</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,30 +18791,30 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45B</t>
+          <t xml:space="preserve">Taagholtvej 170</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522709</t>
+          <t xml:space="preserve">1403213</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912369</t>
+          <t xml:space="preserve">311918197</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,30 +18866,30 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 46</t>
+          <t xml:space="preserve">Torvegade 15</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9870</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5525100</t>
+          <t xml:space="preserve">1800354</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J252">
-        <v>1334</v>
+        <v>940</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918196</t>
+          <t xml:space="preserve">311918198</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18941,17 +18941,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taagholtvej 170</t>
+          <t xml:space="preserve">Vanggårdsgade 10B</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403213</t>
+          <t xml:space="preserve">7075274</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -18960,11 +18960,11 @@
         </is>
       </c>
       <c r="J253">
-        <v>407</v>
+        <v>117</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918197</t>
+          <t xml:space="preserve">311918201</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19016,17 +19016,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 15</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">9870</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800354</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -19035,11 +19035,11 @@
         </is>
       </c>
       <c r="J254">
-        <v>940</v>
+        <v>251</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918198</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19091,30 +19091,30 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanggårdsgade 10B</t>
+          <t xml:space="preserve">Vellingshøjvej 391</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">7075274</t>
+          <t xml:space="preserve">8719304</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J255">
-        <v>117</v>
+        <v>567</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918201</t>
+          <t xml:space="preserve">311918172</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Vellingshøjvej 391A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">3167523</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,11 +19185,11 @@
         </is>
       </c>
       <c r="J256">
-        <v>251</v>
+        <v>427</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311918170</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391</t>
+          <t xml:space="preserve">Idræts Alle 45B</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,20 +19251,20 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">8719304</t>
+          <t xml:space="preserve">5522709</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>567</v>
+        <v>112</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918172</t>
+          <t xml:space="preserve">311921769</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,17 +19316,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vellingshøjvej 391A</t>
+          <t xml:space="preserve">Skagerakvej 2</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9850</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3167523</t>
+          <t xml:space="preserve">3178269</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -19335,11 +19335,11 @@
         </is>
       </c>
       <c r="J258">
-        <v>427</v>
+        <v>518</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918170</t>
+          <t xml:space="preserve">311921781</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-08-26</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 45B</t>
+          <t xml:space="preserve">Elsagervej 27A</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522709</t>
+          <t xml:space="preserve">7871638</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -19410,11 +19410,11 @@
         </is>
       </c>
       <c r="J259">
-        <v>112</v>
+        <v>1723</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921769</t>
+          <t xml:space="preserve">311922371</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,17 +19466,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skagerakvej 2</t>
+          <t xml:space="preserve">Elsagervej 44</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9850</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3178269</t>
+          <t xml:space="preserve">5522933</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -19485,11 +19485,11 @@
         </is>
       </c>
       <c r="J260">
-        <v>518</v>
+        <v>1040</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311921781</t>
+          <t xml:space="preserve">311922368</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-26</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 27A</t>
+          <t xml:space="preserve">Frederikshavnsvej 70B</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,20 +19551,20 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">7871638</t>
+          <t xml:space="preserve">5526485</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J261">
-        <v>1723</v>
+        <v>149</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922371</t>
+          <t xml:space="preserve">311922281</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 44</t>
+          <t xml:space="preserve">Georg Jensens Vej 12</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5522933</t>
+          <t xml:space="preserve">5524990</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -19635,11 +19635,11 @@
         </is>
       </c>
       <c r="J262">
-        <v>1040</v>
+        <v>2910</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922368</t>
+          <t xml:space="preserve">311922280</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederikshavnsvej 70B</t>
+          <t xml:space="preserve">Grønningen 8</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,20 +19701,20 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526485</t>
+          <t xml:space="preserve">7002365</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J263">
-        <v>149</v>
+        <v>367</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922281</t>
+          <t xml:space="preserve">311922282</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georg Jensens Vej 12</t>
+          <t xml:space="preserve">Tjørnevej 6</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5524990</t>
+          <t xml:space="preserve">7010644</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -19785,11 +19785,11 @@
         </is>
       </c>
       <c r="J264">
-        <v>2910</v>
+        <v>380</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922280</t>
+          <t xml:space="preserve">311922366</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 8</t>
+          <t xml:space="preserve">Aage Holms Vej 8</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">7002365</t>
+          <t xml:space="preserve">9938684</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,11 +19860,11 @@
         </is>
       </c>
       <c r="J265">
-        <v>367</v>
+        <v>4353</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922282</t>
+          <t xml:space="preserve">311922647</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,17 +19916,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevej 6</t>
+          <t xml:space="preserve">Hovedgaden 116A</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9760</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010644</t>
+          <t xml:space="preserve">1800942</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,11 +19935,11 @@
         </is>
       </c>
       <c r="J266">
-        <v>380</v>
+        <v>763</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922366</t>
+          <t xml:space="preserve">311922848</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aage Holms Vej 8</t>
+          <t xml:space="preserve">Vester Thirupvej 55A</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">9938684</t>
+          <t xml:space="preserve">10014113</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,11 +20010,11 @@
         </is>
       </c>
       <c r="J267">
-        <v>4353</v>
+        <v>448</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922647</t>
+          <t xml:space="preserve">311922665</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 116A</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,20 +20076,20 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800942</t>
+          <t xml:space="preserve">3214543</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J268">
-        <v>763</v>
+        <v>375</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922848</t>
+          <t xml:space="preserve">311923108</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Thirupvej 55A</t>
+          <t xml:space="preserve">Grønnevold 10</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">10014113</t>
+          <t xml:space="preserve">5526489</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -20160,11 +20160,11 @@
         </is>
       </c>
       <c r="J269">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922665</t>
+          <t xml:space="preserve">311925965</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vester Hedevej 251</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">9760</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">3214543</t>
+          <t xml:space="preserve">5526510</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J270">
-        <v>375</v>
+        <v>258</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923108</t>
+          <t xml:space="preserve">311925892</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-15</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,30 +20291,30 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevold 10</t>
+          <t xml:space="preserve">Vrenstedvej 54</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">9800</t>
+          <t xml:space="preserve">9480</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526489</t>
+          <t xml:space="preserve">9980081</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J271">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925965</t>
+          <t xml:space="preserve">311925986</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Hedevej 251</t>
+          <t xml:space="preserve">Elsagervej 25</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5526510</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -20385,11 +20385,11 @@
         </is>
       </c>
       <c r="J272">
-        <v>258</v>
+        <v>1934</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925892</t>
+          <t xml:space="preserve">311926208</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-15</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,17 +20441,17 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vrenstedvej 54</t>
+          <t xml:space="preserve">Elsagervej 25</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480</t>
+          <t xml:space="preserve">9800</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980081</t>
+          <t xml:space="preserve">1808683</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -20460,11 +20460,11 @@
         </is>
       </c>
       <c r="J273">
-        <v>560</v>
+        <v>167</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925986</t>
+          <t xml:space="preserve">311926230</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-15</t>
+          <t xml:space="preserve">2036-09-16</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25</t>
+          <t xml:space="preserve">Elsagervej 25A</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20531,11 +20531,11 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J274">
-        <v>1934</v>
+        <v>171</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25</t>
+          <t xml:space="preserve">Elsagervej 25B</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20606,15 +20606,15 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J275">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926230</t>
+          <t xml:space="preserve">311926208</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25A</t>
+          <t xml:space="preserve">Slettingenvej 51</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,20 +20676,20 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">1403342</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J276">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926208</t>
+          <t xml:space="preserve">311931975</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-16</t>
+          <t xml:space="preserve">2036-10-15</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsagervej 25B</t>
+          <t xml:space="preserve">Slettingenvej 51</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20751,20 +20751,20 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808683</t>
+          <t xml:space="preserve">1403342</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J277">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926208</t>
+          <t xml:space="preserve">311931976</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-16</t>
+          <t xml:space="preserve">2036-10-15</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
